--- a/(intro stat) dataanalytics_assessment_2441_1683115730_ans.xlsx
+++ b/(intro stat) dataanalytics_assessment_2441_1683115730_ans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DA COURSSE\ASSESSMENT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6EC0184-3E2C-433D-86A2-07085B252FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A58F37-E3B9-40FE-9F4B-49CBE184CE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -248,15 +248,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -555,18 +555,18 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14" t="s">
+      <c r="B3" s="17"/>
+      <c r="C3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14" t="s">
+      <c r="D3" s="17"/>
+      <c r="E3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="14"/>
+      <c r="F3" s="17"/>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -837,17 +837,15 @@
       <c r="B17" s="7"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="17">
-        <f>_xlfn.VAR.P(B5:B16,D5:D16,F5:F16)</f>
-        <v>6170524.6913580243</v>
-      </c>
       <c r="C18" s="2"/>
       <c r="D18" s="11"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="11"/>
+      <c r="E18" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="15">
+        <f>_xlfn.VAR.P(F5:F16)</f>
+        <v>5326388.888888889</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
@@ -867,18 +865,18 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15" t="s">
+      <c r="B22" s="18"/>
+      <c r="C22" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15" t="s">
+      <c r="D22" s="18"/>
+      <c r="E22" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="15"/>
+      <c r="F22" s="18"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
@@ -1060,13 +1058,13 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
+    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E33" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="18">
-        <f>_xlfn.VAR.S(B24:B31,D24:D31,F24:F31)</f>
-        <v>9.2619047619047628</v>
+      <c r="F33" s="16">
+        <f>_xlfn.VAR.S(F24:F31)</f>
+        <v>3.3333333333333335</v>
       </c>
     </row>
   </sheetData>
